--- a/Api/OC-API-TEST_CAUSE.xlsx
+++ b/Api/OC-API-TEST_CAUSE.xlsx
@@ -5,16 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed\Desktop\MANUAL PROJECT\opencart\final fill\API\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed\IdeaProjects\OpenCart-E2E-Testing\Api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BE62E2-F8A3-4545-8162-97C23270BD22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CE5D0A-B79A-4E20-967C-936F2D34EC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Test Cases" sheetId="1" r:id="rId1"/>
-    <sheet name="📊 Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="164">
   <si>
     <t>📋  OpenCart API — Test Cases</t>
   </si>
@@ -203,9 +202,6 @@
 • Error message indicates authentication failure due to missing username.</t>
   </si>
   <si>
-    <t>TC-003B</t>
-  </si>
-  <si>
     <t>Login — Empty Credentials (Blank Username &amp; Key)</t>
   </si>
   <si>
@@ -598,68 +594,17 @@
     <t>Response contains 'success' property with message including 'Shipping address'</t>
   </si>
   <si>
-    <t>📊  Test Cases — Summary</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Total Test Cases</t>
-  </si>
-  <si>
-    <t>Critical Priority</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>High Priority</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Medium Priority</t>
-  </si>
-  <si>
-    <t>Modules Covered</t>
-  </si>
-  <si>
-    <t>Low Priority</t>
-  </si>
-  <si>
-    <t>Positive Tests</t>
-  </si>
-  <si>
-    <t>Pass Rate</t>
-  </si>
-  <si>
-    <t>76%</t>
-  </si>
-  <si>
-    <t>Negative Tests</t>
-  </si>
-  <si>
-    <t>Fail Rate</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
     <t>Expected Status Code</t>
+  </si>
+  <si>
+    <t>TC-021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,19 +650,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -796,7 +728,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -804,100 +736,70 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB0C4DE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB0C4DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB0C4DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0C4DE"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1174,1066 +1076,1066 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="55.6640625" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="44" style="18" customWidth="1"/>
+    <col min="8" max="8" width="44" style="12" customWidth="1"/>
     <col min="9" max="9" width="36" customWidth="1"/>
     <col min="10" max="10" width="44" customWidth="1"/>
     <col min="11" max="11" width="26.109375" customWidth="1"/>
     <col min="12" max="12" width="44" customWidth="1"/>
-    <col min="13" max="13" width="44" style="21" customWidth="1"/>
+    <col min="13" max="13" width="44" style="15" customWidth="1"/>
     <col min="14" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="18" style="18" customWidth="1"/>
+    <col min="15" max="15" width="18" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
     </row>
     <row r="2" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="L2" s="7" t="s">
+      <c r="K2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="N2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="20" t="s">
+      <c r="M4" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="N4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="O4" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="19" t="s">
+      <c r="M5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O5" s="16" t="s">
+      <c r="O5" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="E6" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="G6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="F8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="14" t="s">
+      <c r="H8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="M6" s="20" t="s">
+      <c r="L8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N6" s="11" t="s">
+      <c r="N8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="17" t="s">
+      <c r="O8" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="9" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="C9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="G9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E10" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="9" t="s">
+      <c r="F10" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="H12" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="M12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" s="19" t="s">
+      <c r="L13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="O14" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="12" t="s">
+    <row r="15" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="G15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E16" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="13" t="s">
+      <c r="F16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="K8" s="14" t="s">
+      <c r="H16" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L8" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="20" t="s">
+      <c r="L16" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="N8" s="11" t="s">
+      <c r="N16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="17" t="s">
+      <c r="O16" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="24" t="s">
+    <row r="17" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="F18" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="H18" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="M9" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O9" s="16" t="s">
+      <c r="L18" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="22" t="s">
+    <row r="19" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E19" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" s="14" t="s">
+      <c r="F21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="M10" s="20" t="s">
+      <c r="L21" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="M21" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="N21" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O10" s="17" t="s">
+      <c r="O21" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="24" t="s">
+    <row r="22" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="10" t="s">
+      <c r="F22" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="N11" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="16" t="s">
+      <c r="L22" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O22" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="22" t="s">
+    <row r="23" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E23" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="G12" s="13" t="s">
+      <c r="F23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="K12" s="14" t="s">
+      <c r="H23" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L12" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="M12" s="20" t="s">
+      <c r="L23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M23" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N23" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="N13" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="M14" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="M15" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N15" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="M16" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="M17" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="N17" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O17" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="M18" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="M19" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O19" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="M20" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="N20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="M21" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O21" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="M22" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="N22" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O22" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="M23" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O23" s="16" t="s">
+      <c r="O23" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2244,130 +2146,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="4">
-        <v>21</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="6">
-        <v>16</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="B5" s="4">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B6" s="6">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="4">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B8" s="6">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>180</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>